--- a/src/Verify.OpenXml.Tests/ExcelCommentTests.HeaderNotes.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/ExcelCommentTests.HeaderNotes.verified.xlsx
@@ -59,6 +59,7 @@
       </c>
     </row>
   </sheetData>
+  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 

--- a/src/Verify.OpenXml.Tests/ExcelCommentTests.HeaderNotes.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/ExcelCommentTests.HeaderNotes.verified.xlsx
@@ -59,7 +59,6 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 
